--- a/resources/reselling/files/reselling-int-inventory-aging-tracker.xlsx
+++ b/resources/reselling/files/reselling-int-inventory-aging-tracker.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,11 +89,6 @@
       <i val="1"/>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -183,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -248,8 +243,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -615,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N309"/>
+  <dimension ref="A1:N307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8247,10 +8240,6 @@
           <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
-    </row>
-    <row r="308"/>
-    <row r="309">
-      <c r="A309" s="29" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/resources/reselling/files/reselling-int-inventory-aging-tracker.xlsx
+++ b/resources/reselling/files/reselling-int-inventory-aging-tracker.xlsx
@@ -178,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,15 +233,6 @@
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,8 +618,8 @@
     <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="63" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Inventory, sell-through and aging tracker (Reselling — Intermediate, ch1/3/7/8)</t>
         </is>
@@ -641,14 +632,14 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="168" customHeight="1">
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>As-of date (tonight):</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Type the actual date, not =TODAY() — the report is a snapshot you can compare week to week.</t>
         </is>
@@ -661,7 +652,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1">
+    <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Item</t>
@@ -8233,11 +8224,10 @@
         <v/>
       </c>
     </row>
-    <row r="306"/>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8250,7 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -8281,7 +8271,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>As of:</t>
@@ -8292,7 +8282,6 @@
         <v/>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -8473,7 +8462,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -8488,7 +8476,6 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -8496,7 +8483,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>Listed items with no date (they can't be aged):</t>
@@ -8511,7 +8498,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>Stock with unknown cost (totals are 'at least'):</t>
@@ -8526,7 +8513,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>Committed from your weekly log:</t>
@@ -8538,7 +8525,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -8557,7 +8543,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="63" customHeight="1">
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>Share of committed:</t>
@@ -8572,7 +8558,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -8587,11 +8572,10 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8596,7 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -8630,7 +8614,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -8653,9 +8636,8 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Cohort: listed on or before the day the window opened, and still unsold then</t>
         </is>
@@ -8676,7 +8658,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -8688,7 +8669,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
@@ -8696,11 +8676,10 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
